--- a/exports/trend_1d/ADANIGREEN_full_report.xlsx
+++ b/exports/trend_1d/ADANIGREEN_full_report.xlsx
@@ -18,9 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -51,10 +53,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -420,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q55"/>
+  <dimension ref="A1:U55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -509,6 +512,26 @@
           <t>candles_held</t>
         </is>
       </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>expiry</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>reached_expiry</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>rule_trades</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>rule_wins</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -534,19 +557,19 @@
         <v>18.65</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>43325</v>
+        <v>43326</v>
       </c>
       <c r="H2" t="n">
-        <v>62.7</v>
+        <v>59.6</v>
       </c>
       <c r="I2" t="n">
         <v>62.52799251351085</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="K2" t="n">
-        <v>148.81</v>
+        <v>136.51</v>
       </c>
       <c r="L2" t="n">
         <v>9.52</v>
@@ -564,7 +587,19 @@
         <v>1</v>
       </c>
       <c r="Q2" t="n">
-        <v>31</v>
+        <v>32</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>43307</v>
+      </c>
+      <c r="S2" t="b">
+        <v>1</v>
+      </c>
+      <c r="T2" t="n">
+        <v>2</v>
+      </c>
+      <c r="U2" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="3">
@@ -591,19 +626,19 @@
         <v>18.5</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>43388</v>
+        <v>43389</v>
       </c>
       <c r="H3" t="n">
-        <v>36.85</v>
+        <v>38.65</v>
       </c>
       <c r="I3" t="n">
         <v>37.78618657693271</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="K3" t="n">
-        <v>38.17</v>
+        <v>35.15</v>
       </c>
       <c r="L3" t="n">
         <v>5.37</v>
@@ -621,7 +656,19 @@
         <v>1</v>
       </c>
       <c r="Q3" t="n">
-        <v>40</v>
+        <v>41</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>43342</v>
+      </c>
+      <c r="S3" t="b">
+        <v>1</v>
+      </c>
+      <c r="T3" t="n">
+        <v>3</v>
+      </c>
+      <c r="U3" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="4">
@@ -648,19 +695,19 @@
         <v>18.65</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>43441</v>
+        <v>43444</v>
       </c>
       <c r="H4" t="n">
-        <v>44.45</v>
+        <v>41.3</v>
       </c>
       <c r="I4" t="n">
         <v>42.52105874110555</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="K4" t="n">
-        <v>15.01</v>
+        <v>6.86</v>
       </c>
       <c r="L4" t="n">
         <v>12.03</v>
@@ -669,7 +716,7 @@
         <v>3.4</v>
       </c>
       <c r="N4" t="n">
-        <v>4.96</v>
+        <v>7.09</v>
       </c>
       <c r="O4" t="n">
         <v>4.88</v>
@@ -678,7 +725,19 @@
         <v>1</v>
       </c>
       <c r="Q4" t="n">
-        <v>35</v>
+        <v>36</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>43398</v>
+      </c>
+      <c r="S4" t="b">
+        <v>1</v>
+      </c>
+      <c r="T4" t="n">
+        <v>3</v>
+      </c>
+      <c r="U4" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="5">
@@ -705,19 +764,19 @@
         <v>20.14</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>43535</v>
+        <v>43536</v>
       </c>
       <c r="H5" t="n">
-        <v>36.15</v>
+        <v>39.1</v>
       </c>
       <c r="I5" t="n">
         <v>37.06672406281492</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="K5" t="n">
-        <v>12.47</v>
+        <v>5.33</v>
       </c>
       <c r="L5" t="n">
         <v>13.32</v>
@@ -726,7 +785,7 @@
         <v>4.73</v>
       </c>
       <c r="N5" t="n">
-        <v>7.38</v>
+        <v>8.16</v>
       </c>
       <c r="O5" t="n">
         <v>-7.09</v>
@@ -735,7 +794,19 @@
         <v>1</v>
       </c>
       <c r="Q5" t="n">
-        <v>64</v>
+        <v>65</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>43461</v>
+      </c>
+      <c r="S5" t="b">
+        <v>1</v>
+      </c>
+      <c r="T5" t="n">
+        <v>4</v>
+      </c>
+      <c r="U5" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="6">
@@ -762,19 +833,19 @@
         <v>17.96</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>43600</v>
+        <v>43601</v>
       </c>
       <c r="H6" t="n">
-        <v>37.5</v>
+        <v>36.6</v>
       </c>
       <c r="I6" t="n">
         <v>37.44224069264662</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="K6" t="n">
-        <v>-4.09</v>
+        <v>-6.39</v>
       </c>
       <c r="L6" t="n">
         <v>11.25</v>
@@ -792,7 +863,19 @@
         <v>1</v>
       </c>
       <c r="Q6" t="n">
-        <v>42</v>
+        <v>43</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>43552</v>
+      </c>
+      <c r="S6" t="b">
+        <v>1</v>
+      </c>
+      <c r="T6" t="n">
+        <v>3</v>
+      </c>
+      <c r="U6" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="7">
@@ -819,22 +902,22 @@
         <v>17.94</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>43605</v>
+        <v>43606</v>
       </c>
       <c r="H7" t="n">
-        <v>43.1</v>
+        <v>43.35</v>
       </c>
       <c r="I7" t="n">
         <v>43.16472909296272</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K7" t="n">
-        <v>-17.76</v>
+        <v>-18.44</v>
       </c>
       <c r="L7" t="n">
-        <v>19.95</v>
+        <v>23.5</v>
       </c>
       <c r="M7" t="n">
         <v>9.630000000000001</v>
@@ -849,7 +932,19 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>3</v>
+        <v>4</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>43615</v>
+      </c>
+      <c r="S7" t="b">
+        <v>0</v>
+      </c>
+      <c r="T7" t="n">
+        <v>1</v>
+      </c>
+      <c r="U7" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -876,19 +971,19 @@
         <v>15.48</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>43697</v>
+        <v>43698</v>
       </c>
       <c r="H8" t="n">
-        <v>45.8</v>
+        <v>44.1</v>
       </c>
       <c r="I8" t="n">
         <v>44.66349806742455</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="K8" t="n">
-        <v>5.65</v>
+        <v>1.73</v>
       </c>
       <c r="L8" t="n">
         <v>10.96</v>
@@ -906,7 +1001,19 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>63</v>
+        <v>64</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>43615</v>
+      </c>
+      <c r="S8" t="b">
+        <v>1</v>
+      </c>
+      <c r="T8" t="n">
+        <v>4</v>
+      </c>
+      <c r="U8" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="9">
@@ -933,22 +1040,22 @@
         <v>15.83</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>43720</v>
+        <v>43721</v>
       </c>
       <c r="H9" t="n">
-        <v>48.9</v>
+        <v>50.25</v>
       </c>
       <c r="I9" t="n">
         <v>49.14985010550719</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K9" t="n">
-        <v>-10.88</v>
+        <v>-13.95</v>
       </c>
       <c r="L9" t="n">
-        <v>13.95</v>
+        <v>14.74</v>
       </c>
       <c r="M9" t="n">
         <v>5.99</v>
@@ -963,7 +1070,19 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>43706</v>
+      </c>
+      <c r="S9" t="b">
+        <v>1</v>
+      </c>
+      <c r="T9" t="n">
+        <v>2</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="10">
@@ -990,19 +1109,19 @@
         <v>14.51</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>43843</v>
+        <v>43844</v>
       </c>
       <c r="H10" t="n">
-        <v>209.55</v>
+        <v>199.1</v>
       </c>
       <c r="I10" t="n">
         <v>205.4331761071252</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="K10" t="n">
-        <v>317.01</v>
+        <v>296.22</v>
       </c>
       <c r="L10" t="n">
         <v>4.48</v>
@@ -1020,7 +1139,19 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>82</v>
+        <v>83</v>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>43734</v>
+      </c>
+      <c r="S10" t="b">
+        <v>1</v>
+      </c>
+      <c r="T10" t="n">
+        <v>5</v>
+      </c>
+      <c r="U10" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="11">
@@ -1047,22 +1178,22 @@
         <v>15.68</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>43867</v>
+        <v>43868</v>
       </c>
       <c r="H11" t="n">
-        <v>202.9</v>
+        <v>213</v>
       </c>
       <c r="I11" t="n">
         <v>210.5090233405036</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K11" t="n">
-        <v>-1.91</v>
+        <v>-6.98</v>
       </c>
       <c r="L11" t="n">
-        <v>4.95</v>
+        <v>6.98</v>
       </c>
       <c r="M11" t="n">
         <v>4.98</v>
@@ -1077,7 +1208,19 @@
         <v>1</v>
       </c>
       <c r="Q11" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R11" s="3" t="n">
+        <v>43860</v>
+      </c>
+      <c r="S11" t="b">
+        <v>1</v>
+      </c>
+      <c r="T11" t="n">
+        <v>2</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="12">
@@ -1104,28 +1247,28 @@
         <v>17.94</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>43886</v>
+        <v>43887</v>
       </c>
       <c r="H12" t="n">
-        <v>180.55</v>
+        <v>171.55</v>
       </c>
       <c r="I12" t="n">
         <v>178.5710876496252</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K12" t="n">
-        <v>-15.23</v>
+        <v>-19.46</v>
       </c>
       <c r="L12" t="n">
-        <v>16.36</v>
+        <v>19.46</v>
       </c>
       <c r="M12" t="n">
-        <v>1.74</v>
+        <v>2.77</v>
       </c>
       <c r="N12" t="n">
-        <v>4.59</v>
+        <v>4.98</v>
       </c>
       <c r="O12" t="n">
         <v>4.98</v>
@@ -1134,7 +1277,19 @@
         <v>1</v>
       </c>
       <c r="Q12" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R12" s="3" t="n">
+        <v>43888</v>
+      </c>
+      <c r="S12" t="b">
+        <v>0</v>
+      </c>
+      <c r="T12" t="n">
+        <v>1</v>
+      </c>
+      <c r="U12" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -1161,19 +1316,19 @@
         <v>19.76</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>43914</v>
+        <v>43915</v>
       </c>
       <c r="H13" t="n">
-        <v>141.3</v>
+        <v>148.1</v>
       </c>
       <c r="I13" t="n">
         <v>146.7640735825213</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="K13" t="n">
-        <v>17.63</v>
+        <v>13.67</v>
       </c>
       <c r="L13" t="n">
         <v>3.67</v>
@@ -1191,7 +1346,19 @@
         <v>1</v>
       </c>
       <c r="Q13" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R13" s="3" t="n">
+        <v>43888</v>
+      </c>
+      <c r="S13" t="b">
+        <v>1</v>
+      </c>
+      <c r="T13" t="n">
+        <v>2</v>
+      </c>
+      <c r="U13" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="14">
@@ -1218,19 +1385,19 @@
         <v>23.45</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>44007</v>
+        <v>44008</v>
       </c>
       <c r="H14" t="n">
-        <v>418.45</v>
+        <v>397.55</v>
       </c>
       <c r="I14" t="n">
         <v>406.7439052931301</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="K14" t="n">
-        <v>182.55</v>
+        <v>168.43</v>
       </c>
       <c r="L14" t="n">
         <v>7.53</v>
@@ -1248,7 +1415,19 @@
         <v>1</v>
       </c>
       <c r="Q14" t="n">
-        <v>61</v>
+        <v>62</v>
+      </c>
+      <c r="R14" s="3" t="n">
+        <v>43916</v>
+      </c>
+      <c r="S14" t="b">
+        <v>1</v>
+      </c>
+      <c r="T14" t="n">
+        <v>5</v>
+      </c>
+      <c r="U14" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="15">
@@ -1275,22 +1454,22 @@
         <v>15.57</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>44018</v>
+        <v>44019</v>
       </c>
       <c r="H15" t="n">
-        <v>394.55</v>
+        <v>413.75</v>
       </c>
       <c r="I15" t="n">
         <v>401.3595118021136</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K15" t="n">
-        <v>0.75</v>
+        <v>-4.07</v>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="M15" t="n">
         <v>4.99</v>
@@ -1305,7 +1484,19 @@
         <v>1</v>
       </c>
       <c r="Q15" t="n">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="R15" s="3" t="n">
+        <v>44042</v>
+      </c>
+      <c r="S15" t="b">
+        <v>0</v>
+      </c>
+      <c r="T15" t="n">
+        <v>1</v>
+      </c>
+      <c r="U15" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -1332,22 +1523,22 @@
         <v>21.81</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>44034</v>
+        <v>44035</v>
       </c>
       <c r="H16" t="n">
-        <v>336</v>
+        <v>320.3</v>
       </c>
       <c r="I16" t="n">
         <v>335.0063723759699</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K16" t="n">
-        <v>-18.79</v>
+        <v>-22.59</v>
       </c>
       <c r="L16" t="n">
-        <v>19.63</v>
+        <v>22.66</v>
       </c>
       <c r="M16" t="n">
         <v>2.3</v>
@@ -1362,7 +1553,19 @@
         <v>1</v>
       </c>
       <c r="Q16" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R16" s="3" t="n">
+        <v>44042</v>
+      </c>
+      <c r="S16" t="b">
+        <v>0</v>
+      </c>
+      <c r="T16" t="n">
+        <v>1</v>
+      </c>
+      <c r="U16" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -1389,28 +1592,28 @@
         <v>21.3</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>44064</v>
+        <v>44067</v>
       </c>
       <c r="H17" t="n">
-        <v>376.55</v>
+        <v>414.2</v>
       </c>
       <c r="I17" t="n">
         <v>382.8437652149101</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="K17" t="n">
-        <v>-17.56</v>
+        <v>-29.32</v>
       </c>
       <c r="L17" t="n">
-        <v>21.29</v>
+        <v>29.32</v>
       </c>
       <c r="M17" t="n">
         <v>3.66</v>
       </c>
       <c r="N17" t="n">
-        <v>8.449999999999999</v>
+        <v>10</v>
       </c>
       <c r="O17" t="n">
         <v>-4.67</v>
@@ -1419,7 +1622,19 @@
         <v>1</v>
       </c>
       <c r="Q17" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R17" s="3" t="n">
+        <v>44042</v>
+      </c>
+      <c r="S17" t="b">
+        <v>1</v>
+      </c>
+      <c r="T17" t="n">
+        <v>2</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="18">
@@ -1446,19 +1661,19 @@
         <v>16.52</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>44174</v>
+        <v>44175</v>
       </c>
       <c r="H18" t="n">
-        <v>1070.1</v>
+        <v>1036.7</v>
       </c>
       <c r="I18" t="n">
         <v>1051.717803896687</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="K18" t="n">
-        <v>158.35</v>
+        <v>150.29</v>
       </c>
       <c r="L18" t="n">
         <v>8.68</v>
@@ -1476,7 +1691,19 @@
         <v>1</v>
       </c>
       <c r="Q18" t="n">
-        <v>76</v>
+        <v>77</v>
+      </c>
+      <c r="R18" s="3" t="n">
+        <v>44070</v>
+      </c>
+      <c r="S18" t="b">
+        <v>1</v>
+      </c>
+      <c r="T18" t="n">
+        <v>5</v>
+      </c>
+      <c r="U18" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="19">
@@ -1503,19 +1730,19 @@
         <v>15.58</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>44230</v>
+        <v>44231</v>
       </c>
       <c r="H19" t="n">
-        <v>1026.7</v>
+        <v>1078</v>
       </c>
       <c r="I19" t="n">
         <v>1057.127990481426</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="K19" t="n">
-        <v>0.96</v>
+        <v>-3.98</v>
       </c>
       <c r="L19" t="n">
         <v>7.46</v>
@@ -1533,7 +1760,19 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>38</v>
+        <v>39</v>
+      </c>
+      <c r="R19" s="3" t="n">
+        <v>44196</v>
+      </c>
+      <c r="S19" t="b">
+        <v>1</v>
+      </c>
+      <c r="T19" t="n">
+        <v>3</v>
+      </c>
+      <c r="U19" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="20">
@@ -1560,19 +1799,19 @@
         <v>14.04</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>44285</v>
+        <v>44286</v>
       </c>
       <c r="H20" t="n">
-        <v>1157.65</v>
+        <v>1104.85</v>
       </c>
       <c r="I20" t="n">
         <v>1124.679107282055</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="K20" t="n">
-        <v>7.39</v>
+        <v>2.49</v>
       </c>
       <c r="L20" t="n">
         <v>4.36</v>
@@ -1590,7 +1829,19 @@
         <v>1</v>
       </c>
       <c r="Q20" t="n">
-        <v>37</v>
+        <v>38</v>
+      </c>
+      <c r="R20" s="3" t="n">
+        <v>44252</v>
+      </c>
+      <c r="S20" t="b">
+        <v>1</v>
+      </c>
+      <c r="T20" t="n">
+        <v>3</v>
+      </c>
+      <c r="U20" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="21">
@@ -1617,19 +1868,19 @@
         <v>19.54</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>44333</v>
+        <v>44334</v>
       </c>
       <c r="H21" t="n">
-        <v>1142.45</v>
+        <v>1198.75</v>
       </c>
       <c r="I21" t="n">
         <v>1151.394386858919</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K21" t="n">
-        <v>-3.4</v>
+        <v>-8.5</v>
       </c>
       <c r="L21" t="n">
         <v>10.74</v>
@@ -1647,7 +1898,19 @@
         <v>1</v>
       </c>
       <c r="Q21" t="n">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="R21" s="3" t="n">
+        <v>44315</v>
+      </c>
+      <c r="S21" t="b">
+        <v>1</v>
+      </c>
+      <c r="T21" t="n">
+        <v>2</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="22">
@@ -1674,28 +1937,28 @@
         <v>11.76</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>44363</v>
+        <v>44364</v>
       </c>
       <c r="H22" t="n">
-        <v>1182.75</v>
+        <v>1123.65</v>
       </c>
       <c r="I22" t="n">
         <v>1180.527067665292</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="K22" t="n">
-        <v>-1.33</v>
+        <v>-6.26</v>
       </c>
       <c r="L22" t="n">
-        <v>3.57</v>
+        <v>6.26</v>
       </c>
       <c r="M22" t="n">
         <v>5</v>
       </c>
       <c r="N22" t="n">
-        <v>3.78</v>
+        <v>5</v>
       </c>
       <c r="O22" t="n">
         <v>4.93</v>
@@ -1704,7 +1967,19 @@
         <v>1</v>
       </c>
       <c r="Q22" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R22" s="3" t="n">
+        <v>44343</v>
+      </c>
+      <c r="S22" t="b">
+        <v>1</v>
+      </c>
+      <c r="T22" t="n">
+        <v>2</v>
+      </c>
+      <c r="U22" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="23">
@@ -1731,25 +2006,25 @@
         <v>16.64</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>44433</v>
+        <v>44434</v>
       </c>
       <c r="H23" t="n">
-        <v>997.15</v>
+        <v>1046.45</v>
       </c>
       <c r="I23" t="n">
         <v>1021.031256944643</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="K23" t="n">
-        <v>11.26</v>
+        <v>6.87</v>
       </c>
       <c r="L23" t="n">
         <v>6.46</v>
       </c>
       <c r="M23" t="n">
-        <v>2.6</v>
+        <v>4.3</v>
       </c>
       <c r="N23" t="n">
         <v>5</v>
@@ -1761,7 +2036,19 @@
         <v>1</v>
       </c>
       <c r="Q23" t="n">
-        <v>48</v>
+        <v>49</v>
+      </c>
+      <c r="R23" s="3" t="n">
+        <v>44371</v>
+      </c>
+      <c r="S23" t="b">
+        <v>1</v>
+      </c>
+      <c r="T23" t="n">
+        <v>3</v>
+      </c>
+      <c r="U23" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="24">
@@ -1788,19 +2075,19 @@
         <v>12.06</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>44693</v>
+        <v>44694</v>
       </c>
       <c r="H24" t="n">
-        <v>2436.8</v>
+        <v>2171.55</v>
       </c>
       <c r="I24" t="n">
         <v>2424.031473337338</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="K24" t="n">
-        <v>132.86</v>
+        <v>107.52</v>
       </c>
       <c r="L24" t="n">
         <v>4.63</v>
@@ -1809,7 +2096,7 @@
         <v>5.41</v>
       </c>
       <c r="N24" t="n">
-        <v>8.119999999999999</v>
+        <v>10.89</v>
       </c>
       <c r="O24" t="n">
         <v>4.94</v>
@@ -1818,7 +2105,19 @@
         <v>1</v>
       </c>
       <c r="Q24" t="n">
-        <v>176</v>
+        <v>177</v>
+      </c>
+      <c r="R24" s="3" t="n">
+        <v>44469</v>
+      </c>
+      <c r="S24" t="b">
+        <v>1</v>
+      </c>
+      <c r="T24" t="n">
+        <v>9</v>
+      </c>
+      <c r="U24" t="n">
+        <v>8</v>
       </c>
     </row>
     <row r="25">
@@ -1845,19 +2144,19 @@
         <v>38.31</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>44750</v>
+        <v>44753</v>
       </c>
       <c r="H25" t="n">
-        <v>1921</v>
+        <v>2207.35</v>
       </c>
       <c r="I25" t="n">
         <v>2070.379394899755</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="K25" t="n">
-        <v>11.54</v>
+        <v>-1.65</v>
       </c>
       <c r="L25" t="n">
         <v>17.2</v>
@@ -1866,7 +2165,7 @@
         <v>3.26</v>
       </c>
       <c r="N25" t="n">
-        <v>5.07</v>
+        <v>14.91</v>
       </c>
       <c r="O25" t="n">
         <v>-10.89</v>
@@ -1875,7 +2174,19 @@
         <v>1</v>
       </c>
       <c r="Q25" t="n">
-        <v>41</v>
+        <v>42</v>
+      </c>
+      <c r="R25" s="3" t="n">
+        <v>44707</v>
+      </c>
+      <c r="S25" t="b">
+        <v>1</v>
+      </c>
+      <c r="T25" t="n">
+        <v>3</v>
+      </c>
+      <c r="U25" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="26">
@@ -1902,19 +2213,19 @@
         <v>19.36</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>44830</v>
+        <v>44831</v>
       </c>
       <c r="H26" t="n">
-        <v>2210.35</v>
+        <v>2146.3</v>
       </c>
       <c r="I26" t="n">
         <v>2202.298907298276</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="K26" t="n">
-        <v>0.14</v>
+        <v>-2.77</v>
       </c>
       <c r="L26" t="n">
         <v>13.43</v>
@@ -1932,7 +2243,19 @@
         <v>1</v>
       </c>
       <c r="Q26" t="n">
-        <v>53</v>
+        <v>54</v>
+      </c>
+      <c r="R26" s="3" t="n">
+        <v>44770</v>
+      </c>
+      <c r="S26" t="b">
+        <v>1</v>
+      </c>
+      <c r="T26" t="n">
+        <v>3</v>
+      </c>
+      <c r="U26" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="27">
@@ -1959,19 +2282,19 @@
         <v>15.73</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>44939</v>
+        <v>44942</v>
       </c>
       <c r="H27" t="n">
-        <v>1915.65</v>
+        <v>2089.8</v>
       </c>
       <c r="I27" t="n">
         <v>2054.020157434754</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="K27" t="n">
-        <v>10.75</v>
+        <v>2.63</v>
       </c>
       <c r="L27" t="n">
         <v>12.05</v>
@@ -1989,7 +2312,19 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>76</v>
+        <v>77</v>
+      </c>
+      <c r="R27" s="3" t="n">
+        <v>44833</v>
+      </c>
+      <c r="S27" t="b">
+        <v>1</v>
+      </c>
+      <c r="T27" t="n">
+        <v>5</v>
+      </c>
+      <c r="U27" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="28">
@@ -2016,22 +2351,22 @@
         <v>13.94</v>
       </c>
       <c r="G28" s="1" t="n">
-        <v>44949</v>
+        <v>44950</v>
       </c>
       <c r="H28" t="n">
-        <v>1931.85</v>
+        <v>1916.8</v>
       </c>
       <c r="I28" t="n">
         <v>1917.079456241445</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K28" t="n">
-        <v>-7.56</v>
+        <v>-8.279999999999999</v>
       </c>
       <c r="L28" t="n">
-        <v>8.539999999999999</v>
+        <v>8.84</v>
       </c>
       <c r="M28" t="n">
         <v>0.42</v>
@@ -2046,7 +2381,19 @@
         <v>1</v>
       </c>
       <c r="Q28" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="R28" s="3" t="n">
+        <v>44951</v>
+      </c>
+      <c r="S28" t="b">
+        <v>0</v>
+      </c>
+      <c r="T28" t="n">
+        <v>1</v>
+      </c>
+      <c r="U28" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="29">
@@ -2073,19 +2420,19 @@
         <v>13.78</v>
       </c>
       <c r="G29" s="1" t="n">
-        <v>44993</v>
+        <v>44994</v>
       </c>
       <c r="H29" t="n">
-        <v>619.25</v>
+        <v>650.2</v>
       </c>
       <c r="I29" t="n">
         <v>621.7582698772568</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="K29" t="n">
-        <v>67.69</v>
+        <v>66.08</v>
       </c>
       <c r="L29" t="n">
         <v>2.47</v>
@@ -2103,7 +2450,19 @@
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="R29" s="3" t="n">
+        <v>44951</v>
+      </c>
+      <c r="S29" t="b">
+        <v>1</v>
+      </c>
+      <c r="T29" t="n">
+        <v>3</v>
+      </c>
+      <c r="U29" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="30">
@@ -2130,19 +2489,19 @@
         <v>19.07</v>
       </c>
       <c r="G30" s="1" t="n">
-        <v>45016</v>
+        <v>45019</v>
       </c>
       <c r="H30" t="n">
-        <v>881.15</v>
+        <v>837.45</v>
       </c>
       <c r="I30" t="n">
         <v>866.679792877004</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="K30" t="n">
-        <v>35.52</v>
+        <v>28.8</v>
       </c>
       <c r="L30" t="n">
         <v>0</v>
@@ -2160,7 +2519,19 @@
         <v>1</v>
       </c>
       <c r="Q30" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R30" s="3" t="n">
+        <v>45014</v>
+      </c>
+      <c r="S30" t="b">
+        <v>1</v>
+      </c>
+      <c r="T30" t="n">
+        <v>2</v>
+      </c>
+      <c r="U30" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="31">
@@ -2187,19 +2558,19 @@
         <v>23.03</v>
       </c>
       <c r="G31" s="1" t="n">
-        <v>45068</v>
+        <v>45069</v>
       </c>
       <c r="H31" t="n">
-        <v>941.75</v>
+        <v>988.8</v>
       </c>
       <c r="I31" t="n">
         <v>971.0391782646815</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="K31" t="n">
-        <v>-12.45</v>
+        <v>-18.07</v>
       </c>
       <c r="L31" t="n">
         <v>19.24</v>
@@ -2217,7 +2588,19 @@
         <v>1</v>
       </c>
       <c r="Q31" t="n">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="R31" s="3" t="n">
+        <v>45043</v>
+      </c>
+      <c r="S31" t="b">
+        <v>1</v>
+      </c>
+      <c r="T31" t="n">
+        <v>2</v>
+      </c>
+      <c r="U31" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="32">
@@ -2244,19 +2627,19 @@
         <v>12.28</v>
       </c>
       <c r="G32" s="1" t="n">
-        <v>45141</v>
+        <v>45142</v>
       </c>
       <c r="H32" t="n">
-        <v>1036</v>
+        <v>1012.55</v>
       </c>
       <c r="I32" t="n">
         <v>1025.774595652657</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="K32" t="n">
-        <v>4.77</v>
+        <v>2.4</v>
       </c>
       <c r="L32" t="n">
         <v>9.210000000000001</v>
@@ -2274,7 +2657,19 @@
         <v>1</v>
       </c>
       <c r="Q32" t="n">
-        <v>52</v>
+        <v>53</v>
+      </c>
+      <c r="R32" s="3" t="n">
+        <v>45071</v>
+      </c>
+      <c r="S32" t="b">
+        <v>1</v>
+      </c>
+      <c r="T32" t="n">
+        <v>4</v>
+      </c>
+      <c r="U32" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="33">
@@ -2301,19 +2696,19 @@
         <v>15.56</v>
       </c>
       <c r="G33" s="1" t="n">
-        <v>45237</v>
+        <v>45238</v>
       </c>
       <c r="H33" t="n">
-        <v>932.15</v>
+        <v>946.65</v>
       </c>
       <c r="I33" t="n">
         <v>934.0686570955364</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="K33" t="n">
-        <v>7.94</v>
+        <v>6.51</v>
       </c>
       <c r="L33" t="n">
         <v>4.91</v>
@@ -2331,7 +2726,19 @@
         <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>64</v>
+        <v>65</v>
+      </c>
+      <c r="R33" s="3" t="n">
+        <v>45169</v>
+      </c>
+      <c r="S33" t="b">
+        <v>1</v>
+      </c>
+      <c r="T33" t="n">
+        <v>4</v>
+      </c>
+      <c r="U33" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="34">
@@ -2358,19 +2765,19 @@
         <v>10.76</v>
       </c>
       <c r="G34" s="1" t="n">
-        <v>45363</v>
+        <v>45364</v>
       </c>
       <c r="H34" t="n">
-        <v>1897.1</v>
+        <v>1725</v>
       </c>
       <c r="I34" t="n">
         <v>1760.416881930803</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="K34" t="n">
-        <v>100.4</v>
+        <v>82.22</v>
       </c>
       <c r="L34" t="n">
         <v>3.87</v>
@@ -2379,7 +2786,7 @@
         <v>4.28</v>
       </c>
       <c r="N34" t="n">
-        <v>5.2</v>
+        <v>9.07</v>
       </c>
       <c r="O34" t="n">
         <v>1.56</v>
@@ -2388,7 +2795,19 @@
         <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>87</v>
+        <v>88</v>
+      </c>
+      <c r="R34" s="3" t="n">
+        <v>45260</v>
+      </c>
+      <c r="S34" t="b">
+        <v>1</v>
+      </c>
+      <c r="T34" t="n">
+        <v>5</v>
+      </c>
+      <c r="U34" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="35">
@@ -2415,19 +2834,19 @@
         <v>18.68</v>
       </c>
       <c r="G35" s="1" t="n">
-        <v>45434</v>
+        <v>45435</v>
       </c>
       <c r="H35" t="n">
-        <v>1866.45</v>
+        <v>1888.8</v>
       </c>
       <c r="I35" t="n">
         <v>1886.840285680511</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="K35" t="n">
-        <v>-8.199999999999999</v>
+        <v>-9.5</v>
       </c>
       <c r="L35" t="n">
         <v>14.49</v>
@@ -2445,7 +2864,19 @@
         <v>1</v>
       </c>
       <c r="Q35" t="n">
-        <v>46</v>
+        <v>47</v>
+      </c>
+      <c r="R35" s="3" t="n">
+        <v>45379</v>
+      </c>
+      <c r="S35" t="b">
+        <v>1</v>
+      </c>
+      <c r="T35" t="n">
+        <v>3</v>
+      </c>
+      <c r="U35" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="36">
@@ -2472,28 +2903,28 @@
         <v>10.22</v>
       </c>
       <c r="G36" s="1" t="n">
-        <v>45446</v>
+        <v>45447</v>
       </c>
       <c r="H36" t="n">
-        <v>2038</v>
+        <v>1646</v>
       </c>
       <c r="I36" t="n">
         <v>1804.279908291811</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K36" t="n">
-        <v>7.9</v>
+        <v>-12.85</v>
       </c>
       <c r="L36" t="n">
-        <v>2.58</v>
+        <v>13.68</v>
       </c>
       <c r="M36" t="n">
         <v>1.14</v>
       </c>
       <c r="N36" t="n">
-        <v>1.86</v>
+        <v>19.23</v>
       </c>
       <c r="O36" t="n">
         <v>1.2</v>
@@ -2502,7 +2933,19 @@
         <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R36" s="3" t="n">
+        <v>45442</v>
+      </c>
+      <c r="S36" t="b">
+        <v>1</v>
+      </c>
+      <c r="T36" t="n">
+        <v>2</v>
+      </c>
+      <c r="U36" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="37">
@@ -2529,19 +2972,19 @@
         <v>32.71</v>
       </c>
       <c r="G37" s="1" t="n">
-        <v>45504</v>
+        <v>45505</v>
       </c>
       <c r="H37" t="n">
-        <v>1847.2</v>
+        <v>1901.95</v>
       </c>
       <c r="I37" t="n">
         <v>1853.228949315728</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="K37" t="n">
-        <v>-12.22</v>
+        <v>-15.55</v>
       </c>
       <c r="L37" t="n">
         <v>23.32</v>
@@ -2559,7 +3002,19 @@
         <v>1</v>
       </c>
       <c r="Q37" t="n">
-        <v>40</v>
+        <v>41</v>
+      </c>
+      <c r="R37" s="3" t="n">
+        <v>45470</v>
+      </c>
+      <c r="S37" t="b">
+        <v>1</v>
+      </c>
+      <c r="T37" t="n">
+        <v>3</v>
+      </c>
+      <c r="U37" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="38">
@@ -2586,19 +3041,19 @@
         <v>11.15</v>
       </c>
       <c r="G38" s="1" t="n">
-        <v>45566</v>
+        <v>45568</v>
       </c>
       <c r="H38" t="n">
-        <v>1884.95</v>
+        <v>1807.8</v>
       </c>
       <c r="I38" t="n">
         <v>1870.797639105386</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="K38" t="n">
-        <v>-0.89</v>
+        <v>-4.95</v>
       </c>
       <c r="L38" t="n">
         <v>12.33</v>
@@ -2616,7 +3071,19 @@
         <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>43</v>
+        <v>44</v>
+      </c>
+      <c r="R38" s="3" t="n">
+        <v>45533</v>
+      </c>
+      <c r="S38" t="b">
+        <v>1</v>
+      </c>
+      <c r="T38" t="n">
+        <v>3</v>
+      </c>
+      <c r="U38" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="39">
@@ -2643,28 +3110,28 @@
         <v>13.16</v>
       </c>
       <c r="G39" s="1" t="n">
-        <v>45624</v>
+        <v>45625</v>
       </c>
       <c r="H39" t="n">
-        <v>1087.2</v>
+        <v>1323.9</v>
       </c>
       <c r="I39" t="n">
         <v>1245.43401100942</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="K39" t="n">
-        <v>39.86</v>
+        <v>26.77</v>
       </c>
       <c r="L39" t="n">
         <v>3.36</v>
       </c>
       <c r="M39" t="n">
-        <v>3.2</v>
+        <v>5.68</v>
       </c>
       <c r="N39" t="n">
-        <v>10</v>
+        <v>21.77</v>
       </c>
       <c r="O39" t="n">
         <v>-4.09</v>
@@ -2673,7 +3140,19 @@
         <v>1</v>
       </c>
       <c r="Q39" t="n">
-        <v>39</v>
+        <v>40</v>
+      </c>
+      <c r="R39" s="3" t="n">
+        <v>45596</v>
+      </c>
+      <c r="S39" t="b">
+        <v>1</v>
+      </c>
+      <c r="T39" t="n">
+        <v>3</v>
+      </c>
+      <c r="U39" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="40">
@@ -2700,28 +3179,28 @@
         <v>33.23</v>
       </c>
       <c r="G40" s="1" t="n">
-        <v>45660</v>
+        <v>45663</v>
       </c>
       <c r="H40" t="n">
-        <v>1038.25</v>
+        <v>982.6</v>
       </c>
       <c r="I40" t="n">
         <v>998.6531728767197</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="K40" t="n">
-        <v>-21.58</v>
+        <v>-25.78</v>
       </c>
       <c r="L40" t="n">
-        <v>23.33</v>
+        <v>25.98</v>
       </c>
       <c r="M40" t="n">
         <v>2.31</v>
       </c>
       <c r="N40" t="n">
-        <v>3.96</v>
+        <v>5.36</v>
       </c>
       <c r="O40" t="n">
         <v>21.77</v>
@@ -2730,7 +3209,19 @@
         <v>1</v>
       </c>
       <c r="Q40" t="n">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="R40" s="3" t="n">
+        <v>45652</v>
+      </c>
+      <c r="S40" t="b">
+        <v>1</v>
+      </c>
+      <c r="T40" t="n">
+        <v>2</v>
+      </c>
+      <c r="U40" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="41">
@@ -2757,25 +3248,25 @@
         <v>19.45</v>
       </c>
       <c r="G41" s="1" t="n">
-        <v>45672</v>
+        <v>45673</v>
       </c>
       <c r="H41" t="n">
-        <v>1035.05</v>
+        <v>1070.25</v>
       </c>
       <c r="I41" t="n">
         <v>1054.942324143713</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K41" t="n">
-        <v>-5.34</v>
+        <v>-8.92</v>
       </c>
       <c r="L41" t="n">
-        <v>9.91</v>
+        <v>14.7</v>
       </c>
       <c r="M41" t="n">
-        <v>3.29</v>
+        <v>6.96</v>
       </c>
       <c r="N41" t="n">
         <v>13.16</v>
@@ -2787,7 +3278,19 @@
         <v>1</v>
       </c>
       <c r="Q41" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R41" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S41" t="b">
+        <v>0</v>
+      </c>
+      <c r="T41" t="n">
+        <v>1</v>
+      </c>
+      <c r="U41" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="42">
@@ -2814,22 +3317,22 @@
         <v>14.79</v>
       </c>
       <c r="G42" s="1" t="n">
-        <v>45701</v>
+        <v>45702</v>
       </c>
       <c r="H42" t="n">
-        <v>913.75</v>
+        <v>884.4</v>
       </c>
       <c r="I42" t="n">
         <v>911.9601956992328</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="K42" t="n">
-        <v>-14.62</v>
+        <v>-17.37</v>
       </c>
       <c r="L42" t="n">
-        <v>16.18</v>
+        <v>18.43</v>
       </c>
       <c r="M42" t="n">
         <v>1.68</v>
@@ -2844,7 +3347,19 @@
         <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R42" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S42" t="b">
+        <v>1</v>
+      </c>
+      <c r="T42" t="n">
+        <v>2</v>
+      </c>
+      <c r="U42" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="43">
@@ -2871,22 +3386,22 @@
         <v>16.34</v>
       </c>
       <c r="G43" s="1" t="n">
-        <v>45735</v>
+        <v>45736</v>
       </c>
       <c r="H43" t="n">
-        <v>911.2</v>
+        <v>923.4</v>
       </c>
       <c r="I43" t="n">
         <v>911.6427860673182</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="K43" t="n">
-        <v>-3.03</v>
+        <v>-4.41</v>
       </c>
       <c r="L43" t="n">
-        <v>4.44</v>
+        <v>4.92</v>
       </c>
       <c r="M43" t="n">
         <v>2.41</v>
@@ -2901,7 +3416,19 @@
         <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R43" s="3" t="n">
+        <v>45715</v>
+      </c>
+      <c r="S43" t="b">
+        <v>1</v>
+      </c>
+      <c r="T43" t="n">
+        <v>2</v>
+      </c>
+      <c r="U43" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="44">
@@ -2928,19 +3455,19 @@
         <v>13.12</v>
       </c>
       <c r="G44" s="1" t="n">
-        <v>45826</v>
+        <v>45827</v>
       </c>
       <c r="H44" t="n">
-        <v>968.9</v>
+        <v>934</v>
       </c>
       <c r="I44" t="n">
         <v>967.8881385404719</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="K44" t="n">
-        <v>4.93</v>
+        <v>1.15</v>
       </c>
       <c r="L44" t="n">
         <v>7.95</v>
@@ -2958,7 +3485,19 @@
         <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>60</v>
+        <v>61</v>
+      </c>
+      <c r="R44" s="3" t="n">
+        <v>45743</v>
+      </c>
+      <c r="S44" t="b">
+        <v>1</v>
+      </c>
+      <c r="T44" t="n">
+        <v>4</v>
+      </c>
+      <c r="U44" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="45">
@@ -2985,22 +3524,22 @@
         <v>11.66</v>
       </c>
       <c r="G45" s="1" t="n">
-        <v>45853</v>
+        <v>45854</v>
       </c>
       <c r="H45" t="n">
-        <v>1033.1</v>
+        <v>1038.6</v>
       </c>
       <c r="I45" t="n">
         <v>1037.85407885789</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="K45" t="n">
-        <v>-10.61</v>
+        <v>-11.2</v>
       </c>
       <c r="L45" t="n">
-        <v>12.09</v>
+        <v>12.37</v>
       </c>
       <c r="M45" t="n">
         <v>1.51</v>
@@ -3015,7 +3554,19 @@
         <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R45" s="3" t="n">
+        <v>45834</v>
+      </c>
+      <c r="S45" t="b">
+        <v>1</v>
+      </c>
+      <c r="T45" t="n">
+        <v>2</v>
+      </c>
+      <c r="U45" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="46">
@@ -3042,22 +3593,22 @@
         <v>6.68</v>
       </c>
       <c r="G46" s="1" t="n">
-        <v>45869</v>
+        <v>45870</v>
       </c>
       <c r="H46" t="n">
-        <v>984.7</v>
+        <v>972.6</v>
       </c>
       <c r="I46" t="n">
         <v>972.8312269380394</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K46" t="n">
-        <v>-5.19</v>
+        <v>-6.35</v>
       </c>
       <c r="L46" t="n">
-        <v>6.32</v>
+        <v>6.8</v>
       </c>
       <c r="M46" t="n">
         <v>2.4</v>
@@ -3072,7 +3623,19 @@
         <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R46" s="3" t="n">
+        <v>45869</v>
+      </c>
+      <c r="S46" t="b">
+        <v>1</v>
+      </c>
+      <c r="T46" t="n">
+        <v>2</v>
+      </c>
+      <c r="U46" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="47">
@@ -3099,28 +3662,28 @@
         <v>10.32</v>
       </c>
       <c r="G47" s="1" t="n">
-        <v>45918</v>
+        <v>45919</v>
       </c>
       <c r="H47" t="n">
-        <v>978.9</v>
+        <v>1030.7</v>
       </c>
       <c r="I47" t="n">
         <v>991.9124393992413</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="K47" t="n">
-        <v>-0.65</v>
+        <v>-5.97</v>
       </c>
       <c r="L47" t="n">
-        <v>3.6</v>
+        <v>10.12</v>
       </c>
       <c r="M47" t="n">
-        <v>1.25</v>
+        <v>4.71</v>
       </c>
       <c r="N47" t="n">
-        <v>3.37</v>
+        <v>5.29</v>
       </c>
       <c r="O47" t="n">
         <v>-1.23</v>
@@ -3129,7 +3692,19 @@
         <v>0</v>
       </c>
       <c r="Q47" t="n">
-        <v>33</v>
+        <v>34</v>
+      </c>
+      <c r="R47" s="3" t="n">
+        <v>45897</v>
+      </c>
+      <c r="S47" t="b">
+        <v>1</v>
+      </c>
+      <c r="T47" t="n">
+        <v>2</v>
+      </c>
+      <c r="U47" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="48">
@@ -3156,19 +3731,19 @@
         <v>7.34</v>
       </c>
       <c r="G48" s="1" t="n">
-        <v>45954</v>
+        <v>45957</v>
       </c>
       <c r="H48" t="n">
-        <v>1031.1</v>
+        <v>1017.1</v>
       </c>
       <c r="I48" t="n">
         <v>1026.095143830456</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="K48" t="n">
-        <v>0.04</v>
+        <v>-1.32</v>
       </c>
       <c r="L48" t="n">
         <v>2.69</v>
@@ -3186,7 +3761,19 @@
         <v>1</v>
       </c>
       <c r="Q48" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R48" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S48" t="b">
+        <v>1</v>
+      </c>
+      <c r="T48" t="n">
+        <v>2</v>
+      </c>
+      <c r="U48" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="49">
@@ -3213,28 +3800,28 @@
         <v>7.68</v>
       </c>
       <c r="G49" s="1" t="n">
-        <v>45958</v>
+        <v>45959</v>
       </c>
       <c r="H49" t="n">
-        <v>1004.2</v>
+        <v>1112.6</v>
       </c>
       <c r="I49" t="n">
         <v>1085.405024463342</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K49" t="n">
-        <v>1.27</v>
+        <v>-9.390000000000001</v>
       </c>
       <c r="L49" t="n">
-        <v>1.03</v>
+        <v>12.57</v>
       </c>
       <c r="M49" t="n">
-        <v>0.33</v>
+        <v>2.37</v>
       </c>
       <c r="N49" t="n">
-        <v>0</v>
+        <v>10.79</v>
       </c>
       <c r="O49" t="n">
         <v>-1.36</v>
@@ -3243,7 +3830,19 @@
         <v>0</v>
       </c>
       <c r="Q49" t="n">
+        <v>3</v>
+      </c>
+      <c r="R49" s="3" t="n">
+        <v>45958</v>
+      </c>
+      <c r="S49" t="b">
+        <v>1</v>
+      </c>
+      <c r="T49" t="n">
         <v>2</v>
+      </c>
+      <c r="U49" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="50">
@@ -3270,22 +3869,22 @@
         <v>12.85</v>
       </c>
       <c r="G50" s="1" t="n">
-        <v>45982</v>
+        <v>45985</v>
       </c>
       <c r="H50" t="n">
-        <v>1030.5</v>
+        <v>1009.4</v>
       </c>
       <c r="I50" t="n">
         <v>1026.706037166223</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="K50" t="n">
-        <v>-7.38</v>
+        <v>-9.279999999999999</v>
       </c>
       <c r="L50" t="n">
-        <v>9.029999999999999</v>
+        <v>9.58</v>
       </c>
       <c r="M50" t="n">
         <v>-0</v>
@@ -3300,7 +3899,19 @@
         <v>1</v>
       </c>
       <c r="Q50" t="n">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="R50" s="3" t="n">
+        <v>45986</v>
+      </c>
+      <c r="S50" t="b">
+        <v>0</v>
+      </c>
+      <c r="T50" t="n">
+        <v>1</v>
+      </c>
+      <c r="U50" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="51">
@@ -3327,28 +3938,28 @@
         <v>11.76</v>
       </c>
       <c r="G51" s="1" t="n">
-        <v>46055</v>
+        <v>46056</v>
       </c>
       <c r="H51" t="n">
-        <v>843.95</v>
+        <v>932.1</v>
       </c>
       <c r="I51" t="n">
         <v>913.4943404329134</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="K51" t="n">
-        <v>16.39</v>
+        <v>7.66</v>
       </c>
       <c r="L51" t="n">
         <v>4.88</v>
       </c>
       <c r="M51" t="n">
-        <v>2.1</v>
+        <v>9.49</v>
       </c>
       <c r="N51" t="n">
-        <v>4.6</v>
+        <v>10.44</v>
       </c>
       <c r="O51" t="n">
         <v>-2.05</v>
@@ -3357,7 +3968,19 @@
         <v>0</v>
       </c>
       <c r="Q51" t="n">
-        <v>49</v>
+        <v>50</v>
+      </c>
+      <c r="R51" s="3" t="n">
+        <v>45986</v>
+      </c>
+      <c r="S51" t="b">
+        <v>1</v>
+      </c>
+      <c r="T51" t="n">
+        <v>4</v>
+      </c>
+      <c r="U51" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="52">
@@ -3384,22 +4007,22 @@
         <v>15.98</v>
       </c>
       <c r="G52" s="1" t="n">
-        <v>46083</v>
+        <v>46085</v>
       </c>
       <c r="H52" t="n">
-        <v>903.55</v>
+        <v>871.95</v>
       </c>
       <c r="I52" t="n">
         <v>884.1256015887191</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="K52" t="n">
-        <v>-3.06</v>
+        <v>-6.45</v>
       </c>
       <c r="L52" t="n">
-        <v>5.56</v>
+        <v>6.98</v>
       </c>
       <c r="M52" t="n">
         <v>3.41</v>
@@ -3414,7 +4037,19 @@
         <v>1</v>
       </c>
       <c r="Q52" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R52" s="3" t="n">
+        <v>46077</v>
+      </c>
+      <c r="S52" t="b">
+        <v>1</v>
+      </c>
+      <c r="T52" t="n">
+        <v>2</v>
+      </c>
+      <c r="U52" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="53">
@@ -3441,28 +4076,28 @@
         <v>12.71</v>
       </c>
       <c r="G53" s="1" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="H53" t="n">
-        <v>925.35</v>
+        <v>1029.65</v>
       </c>
       <c r="I53" t="n">
         <v>925.9196591084458</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="K53" t="n">
-        <v>-6.12</v>
+        <v>-18.09</v>
       </c>
       <c r="L53" t="n">
-        <v>7.22</v>
+        <v>20.03</v>
       </c>
       <c r="M53" t="n">
-        <v>2.86</v>
+        <v>4.72</v>
       </c>
       <c r="N53" t="n">
-        <v>7.61</v>
+        <v>11.27</v>
       </c>
       <c r="O53" t="n">
         <v>-3.5</v>
@@ -3471,7 +4106,19 @@
         <v>0</v>
       </c>
       <c r="Q53" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R53" s="3" t="n">
+        <v>46111</v>
+      </c>
+      <c r="S53" t="b">
+        <v>1</v>
+      </c>
+      <c r="T53" t="n">
+        <v>2</v>
+      </c>
+      <c r="U53" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="54">
@@ -3498,19 +4145,19 @@
         <v>16.04</v>
       </c>
       <c r="G54" s="1" t="n">
-        <v>46225</v>
+        <v>46226</v>
       </c>
       <c r="H54" t="n">
-        <v>1472.3</v>
+        <v>1379.9</v>
       </c>
       <c r="I54" t="n">
         <v>1421.113785142609</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="K54" t="n">
-        <v>42.99</v>
+        <v>34.02</v>
       </c>
       <c r="L54" t="n">
         <v>5.99</v>
@@ -3519,7 +4166,7 @@
         <v>3.16</v>
       </c>
       <c r="N54" t="n">
-        <v>5.74</v>
+        <v>6.28</v>
       </c>
       <c r="O54" t="n">
         <v>11.27</v>
@@ -3528,7 +4175,19 @@
         <v>1</v>
       </c>
       <c r="Q54" t="n">
-        <v>72</v>
+        <v>73</v>
+      </c>
+      <c r="R54" s="3" t="n">
+        <v>46140</v>
+      </c>
+      <c r="S54" t="b">
+        <v>1</v>
+      </c>
+      <c r="T54" t="n">
+        <v>4</v>
+      </c>
+      <c r="U54" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="55">
@@ -3579,6 +4238,14 @@
       <c r="Q55" t="n">
         <v>67</v>
       </c>
+      <c r="R55" s="3" t="n">
+        <v>46231</v>
+      </c>
+      <c r="S55" t="b">
+        <v>1</v>
+      </c>
+      <c r="T55" t="inlineStr"/>
+      <c r="U55" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -7143,7 +7810,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>54.2</v>
+        <v>55.5</v>
       </c>
     </row>
     <row r="6">
@@ -7153,7 +7820,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="7">
@@ -7163,7 +7830,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>259</v>
+        <v>260</v>
       </c>
     </row>
     <row r="8">
@@ -7173,7 +7840,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9">
@@ -7183,7 +7850,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="10">
@@ -7193,7 +7860,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="11">
@@ -7203,7 +7870,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="12">
@@ -7213,7 +7880,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="13">
@@ -7223,7 +7890,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>35.8</v>
+        <v>34</v>
       </c>
     </row>
     <row r="14">
@@ -7233,7 +7900,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>22.47</v>
+        <v>16.06</v>
       </c>
     </row>
     <row r="15">
@@ -7243,7 +7910,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>39.43</v>
+        <v>32.17</v>
       </c>
     </row>
     <row r="16">
@@ -7253,7 +7920,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>4.87</v>
+        <v>-0.67</v>
       </c>
     </row>
     <row r="17">
@@ -7263,7 +7930,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>317.01</v>
+        <v>296.22</v>
       </c>
     </row>
     <row r="18">
@@ -7273,7 +7940,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>54.7</v>
+        <v>41.5</v>
       </c>
     </row>
     <row r="19">
@@ -7283,7 +7950,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>9.199999999999999</v>
+        <v>10.75</v>
       </c>
     </row>
     <row r="20">
@@ -7293,7 +7960,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>7.95</v>
+        <v>9.52</v>
       </c>
     </row>
     <row r="21">
@@ -7303,7 +7970,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>23.33</v>
+        <v>29.32</v>
       </c>
     </row>
     <row r="22">
@@ -7313,7 +7980,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>35</v>
+        <v>40</v>
       </c>
     </row>
     <row r="23">
@@ -7323,7 +7990,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
     </row>
     <row r="24">
@@ -7333,7 +8000,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>3.52</v>
+        <v>3.96</v>
       </c>
     </row>
     <row r="25">
@@ -7353,7 +8020,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>6</v>
+        <v>7.43</v>
       </c>
     </row>
     <row r="27">
@@ -7363,7 +8030,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>15.24</v>
+        <v>21.77</v>
       </c>
     </row>
     <row r="28">
@@ -7373,7 +8040,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>43</v>
+        <v>48</v>
       </c>
     </row>
     <row r="29">
